--- a/documents/ProductBacklog_group51.xlsx
+++ b/documents/ProductBacklog_group51.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <si>
     <t xml:space="preserve">Story ID</t>
   </si>
@@ -56,21 +56,15 @@
   <si>
     <t xml:space="preserve">As a TA applicant
 I want to create an applicant profile
-So that I can provide my personal and academic information for recruitment.</t>
+So that I can provide my personal and academic information.</t>
   </si>
   <si>
     <t>Must</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. User can register with name, email and student ID
-2. Profile information is saved to the system
-3. User can edit profile after creation</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t xml:space="preserve">1. User can create profile
+2. Information saved
+3. Profile editable</t>
   </si>
   <si>
     <t>2026-03-20</t>
@@ -80,6 +74,22 @@
   </si>
   <si>
     <t>US-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login to system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a TA applicant
+I want to log into the system
+So that I can access my account.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. User enters credentials
+2. System validates login
+3. Dashboard displayed</t>
+  </si>
+  <si>
+    <t>US-03</t>
   </si>
   <si>
     <t xml:space="preserve">Upload CV</t>
@@ -87,34 +97,31 @@
   <si>
     <t xml:space="preserve">As a TA applicant
 I want to upload my CV
-So that module organisers can review my qualifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. User can upload a PDF CV
-2. File is stored successfully
-3. Uploaded CV can be viewed later</t>
-  </si>
-  <si>
-    <t>US-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Browse available jobs</t>
+So that recruiters can review my qualifications.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Upload PDF file
+2. File stored successfully
+3. File viewable later</t>
+  </si>
+  <si>
+    <t>US-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browse jobs</t>
   </si>
   <si>
     <t xml:space="preserve">As a TA applicant
-I want to browse available TA jobs
-So that I can find suitable opportunities.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Job list is displayed
-2. Each job shows module name and requirements
-3. Users can view job details</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>US-04</t>
+I want to browse available jobs
+So that I can find opportunities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Job list displayed
+2. Job description visible
+3. List updates automatically</t>
+  </si>
+  <si>
+    <t>US-05</t>
   </si>
   <si>
     <t xml:space="preserve">Apply for job</t>
@@ -125,31 +132,28 @@
 So that I can be considered for the position.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Applicant can submit application
-2. Application record is stored
-3. Confirmation message is displayed</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>US-05</t>
+    <t xml:space="preserve">1. Application submitted
+2. Confirmation shown
+3. Record saved</t>
+  </si>
+  <si>
+    <t>US-06</t>
   </si>
   <si>
     <t xml:space="preserve">Check application status</t>
   </si>
   <si>
     <t xml:space="preserve">As a TA applicant
-I want to check my application status
-So that I know whether I am selected.</t>
+I want to check application status
+So that I can manage my job applications.</t>
   </si>
   <si>
     <t>Should</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Applicant can see application status
-2. Status includes pending, accepted, rejected
-3. Status updates when MO makes decision</t>
+    <t xml:space="preserve">1. Feature accessible
+2. Data updates correctly
+3. Confirmation displayed</t>
   </si>
   <si>
     <t>2026-03-28</t>
@@ -158,96 +162,502 @@
     <t>2026-04-05</t>
   </si>
   <si>
-    <t>US-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post job</t>
+    <t>US-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Withdraw application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a TA applicant
+I want to withdraw application
+So that I can manage my job applications.</t>
+  </si>
+  <si>
+    <t>US-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View job details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a TA applicant
+I want to view job details
+So that I can manage my job applications.</t>
+  </si>
+  <si>
+    <t>US-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a TA applicant
+I want to search jobs
+So that I can manage my job applications.</t>
+  </si>
+  <si>
+    <t>US-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter jobs by module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a TA applicant
+I want to filter jobs by module
+So that I can manage my job applications.</t>
+  </si>
+  <si>
+    <t>US-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receive notification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a TA applicant
+I want to receive notification
+So that I can manage my job applications.</t>
+  </si>
+  <si>
+    <t>US-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a TA applicant
+I want to edit profile
+So that I can manage my job applications.</t>
+  </si>
+  <si>
+    <t>US-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a TA applicant
+I want to delete profile
+So that I can manage my job applications.</t>
+  </si>
+  <si>
+    <t>US-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save favourite jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a TA applicant
+I want to save favourite jobs
+So that I can manage my job applications.</t>
+  </si>
+  <si>
+    <t>US-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View application history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a TA applicant
+I want to view application history
+So that I can manage my job applications.</t>
+  </si>
+  <si>
+    <t>US-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post TA job</t>
   </si>
   <si>
     <t xml:space="preserve">As a module organiser
-I want to post TA job opportunities
-So that students can apply.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. MO can create job listing
-2. Job description and requirements are saved
-3. Job appears in job list</t>
-  </si>
-  <si>
-    <t>US-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select applicants</t>
+I want to post ta job
+So that I can manage recruitment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. MO can perform action
+2. Changes saved
+3. UI updated</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>US-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit job post</t>
   </si>
   <si>
     <t xml:space="preserve">As a module organiser
-I want to select applicants
-So that I can recruit suitable teaching assistants.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. MO can view applicant list
-2. MO can mark applicant as selected
-3. Selected status updates applicant record</t>
-  </si>
-  <si>
-    <t>US-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View workload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an administrator
-I want to check TA workload
-So that no TA is overloaded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Admin can view TA assignments
-2. System shows number of assigned jobs
-3. Warning displayed if workload exceeds limit</t>
-  </si>
-  <si>
-    <t>US-09</t>
+I want to edit job post
+So that I can manage recruitment.</t>
+  </si>
+  <si>
+    <t>US-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete job post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a module organiser
+I want to delete job post
+So that I can manage recruitment.</t>
+  </si>
+  <si>
+    <t>US-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View applicants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a module organiser
+I want to view applicants
+So that I can manage recruitment.</t>
+  </si>
+  <si>
+    <t>US-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort applicants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a module organiser
+I want to sort applicants
+So that I can manage recruitment.</t>
+  </si>
+  <si>
+    <t>US-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shortlist applicants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a module organiser
+I want to shortlist applicants
+So that I can manage recruitment.</t>
+  </si>
+  <si>
+    <t>US-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accept applicant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a module organiser
+I want to accept applicant
+So that I can manage recruitment.</t>
+  </si>
+  <si>
+    <t>US-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reject applicant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a module organiser
+I want to reject applicant
+So that I can manage recruitment.</t>
+  </si>
+  <si>
+    <t>US-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send decision notification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a module organiser
+I want to send decision notification
+So that I can manage recruitment.</t>
+  </si>
+  <si>
+    <t>US-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download applicant CV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a module organiser
+I want to download applicant cv
+So that I can manage recruitment.</t>
+  </si>
+  <si>
+    <t>US-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View TA workload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to view ta workload
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>Could</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Feature implemented
+2. Output correct
+3. System stable</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>US-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate workload report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to generate workload report
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to admin dashboard
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manage users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to manage users
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to assign roles
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System activity log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to system activity log
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-32</t>
   </si>
   <si>
     <t xml:space="preserve">Skill matching</t>
   </si>
   <si>
-    <t xml:space="preserve">As a module organiser
-I want the system to match applicant skills with job requirements
-So that I can quickly identify suitable candidates.</t>
-  </si>
-  <si>
-    <t>Could</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. System analyses CV text
-2. Skills are matched with job requirements
-3. Match score is displayed</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>US-10</t>
+    <t xml:space="preserve">As a system user
+I want to skill matching
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommend applicants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to recommend applicants
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-34</t>
   </si>
   <si>
     <t xml:space="preserve">Identify missing skills</t>
   </si>
   <si>
-    <t xml:space="preserve">As a TA applicant
-I want the system to identify missing skills
-So that I can improve my qualifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. System compares CV with job requirements
-2. Missing skills are highlighted
-3. Suggestions are displayed</t>
+    <t xml:space="preserve">As a system user
+I want to identify missing skills
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggest training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to suggest training
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI ranking of applicants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to ai ranking of applicants
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Export recruitment report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to export recruitment report
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System availability monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to system availability monitoring
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile interface support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to mobile interface support
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-language interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to multi-language interface
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secure data storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to secure data storage
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup system data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to backup system data
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore system data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to restore system data
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance optimisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to performance optimisation
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System help page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to system help page
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User feedback submission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to user feedback submission
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin review feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to admin review feedback
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notification settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to notification settings
+So that the recruitment system works efficiently.</t>
+  </si>
+  <si>
+    <t>US-49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email alerts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a system user
+I want to email alerts
+So that the recruitment system works efficiently.</t>
   </si>
 </sst>
 </file>
@@ -310,10 +720,20 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -817,6 +1237,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="26.28125"/>
+  </cols>
   <sheetData>
     <row r="1" ht="48.75" customHeight="1">
       <c r="A1" s="1" t="s">
@@ -850,207 +1273,207 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="14.25">
+    <row r="2" ht="34.100000000000001" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
+      <c r="G2" s="2">
+        <v>3</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="34.100000000000001" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" ht="14.25">
-      <c r="A3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>16</v>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="34.100000000000001" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>27</v>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="34.100000000000001" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>32</v>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="2">
+        <v>3</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="34.100000000000001" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="2">
+        <v>5</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="34.100000000000001" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" ht="34.100000000000001" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
@@ -1060,27 +1483,27 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" ht="14.25">
+    <row r="9" ht="34.100000000000001" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>16</v>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
@@ -1090,64 +1513,1234 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" ht="14.25">
+    <row r="10" ht="34.100000000000001" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="34.100000000000001" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" ht="34.100000000000001" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="2">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="34.100000000000001" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" ht="34.100000000000001" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>59</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="2">
+        <v>3</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="34.100000000000001" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="2">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" ht="34.100000000000001" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="2">
+        <v>3</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="34.100000000000001" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="2">
+        <v>5</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" ht="34.100000000000001" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="2">
+        <v>5</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" ht="34.100000000000001" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2">
+        <v>3</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="2">
+        <v>5</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" ht="34.100000000000001" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="2">
+        <v>5</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" ht="34.100000000000001" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="2">
+        <v>5</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" ht="34.100000000000001" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="2">
+        <v>5</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" ht="34.100000000000001" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="2">
+        <v>5</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" ht="34.100000000000001" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2">
+        <v>3</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="2">
+        <v>5</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" ht="34.100000000000001" customHeight="1">
+      <c r="A25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="2">
+        <v>5</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" ht="34.100000000000001" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2">
+        <v>5</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" ht="34.100000000000001" customHeight="1">
+      <c r="A27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27" s="2">
+        <v>5</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" ht="34.100000000000001" customHeight="1">
+      <c r="A28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="2">
+        <v>5</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" ht="34.100000000000001" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="2">
+        <v>4</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" s="2">
+        <v>5</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" ht="34.100000000000001" customHeight="1">
+      <c r="A30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="2">
+        <v>4</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" s="2">
+        <v>5</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" ht="34.100000000000001" customHeight="1">
+      <c r="A31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="2">
+        <v>4</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G31" s="2">
+        <v>5</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" ht="34.100000000000001" customHeight="1">
+      <c r="A32" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="2">
+        <v>4</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G32" s="2">
+        <v>5</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" ht="34.100000000000001" customHeight="1">
+      <c r="A33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="2">
+        <v>4</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G33" s="2">
+        <v>5</v>
+      </c>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" ht="34.100000000000001" customHeight="1">
+      <c r="A34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="2">
+        <v>4</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G34" s="2">
+        <v>5</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" ht="34.100000000000001" customHeight="1">
+      <c r="A35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" s="2">
+        <v>4</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G35" s="2">
+        <v>5</v>
+      </c>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" ht="34.100000000000001" customHeight="1">
+      <c r="A36" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" s="2">
+        <v>4</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G36" s="2">
+        <v>5</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" ht="34.100000000000001" customHeight="1">
+      <c r="A37" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" s="2">
+        <v>4</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G37" s="2">
+        <v>5</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" ht="34.100000000000001" customHeight="1">
+      <c r="A38" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="2">
+        <v>4</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G38" s="2">
+        <v>5</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" ht="34.100000000000001" customHeight="1">
+      <c r="A39" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" s="2">
+        <v>4</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="2">
+        <v>5</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" ht="34.100000000000001" customHeight="1">
+      <c r="A40" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="2">
+        <v>4</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="2">
+        <v>5</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" ht="34.100000000000001" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="2">
+        <v>4</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G41" s="2">
+        <v>5</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42" ht="34.100000000000001" customHeight="1">
+      <c r="A42" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="2">
+        <v>4</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" s="2">
+        <v>5</v>
+      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" ht="34.100000000000001" customHeight="1">
+      <c r="A43" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" s="2">
+        <v>4</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G43" s="2">
+        <v>5</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" ht="34.100000000000001" customHeight="1">
+      <c r="A44" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="2">
+        <v>4</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G44" s="2">
+        <v>5</v>
+      </c>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45" ht="34.100000000000001" customHeight="1">
+      <c r="A45" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="2">
+        <v>4</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G45" s="2">
+        <v>5</v>
+      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" ht="34.100000000000001" customHeight="1">
+      <c r="A46" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="2">
+        <v>4</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="2">
+        <v>5</v>
+      </c>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" ht="34.100000000000001" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="2">
+        <v>4</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G47" s="2">
+        <v>5</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" ht="34.100000000000001" customHeight="1">
+      <c r="A48" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48" s="2">
+        <v>4</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G48" s="2">
+        <v>5</v>
+      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" ht="34.100000000000001" customHeight="1">
+      <c r="A49" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G49" s="2">
+        <v>5</v>
+      </c>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="50" ht="34.100000000000001" customHeight="1">
+      <c r="A50" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E50" s="2">
+        <v>4</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G50" s="2">
+        <v>5</v>
+      </c>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/documents/ProductBacklog_group51.xlsx
+++ b/documents/ProductBacklog_group51.xlsx
@@ -1,28 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView windowWidth="21600" windowHeight="9555"/>
   </bookViews>
   <sheets>
-    <sheet name="Product Backlog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
-  <si>
-    <t xml:space="preserve">Story ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Story Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
+  <si>
+    <t>Story ID</t>
+  </si>
+  <si>
+    <t>Story Name</t>
   </si>
   <si>
     <t>Description</t>
@@ -31,10 +41,10 @@
     <t>Priority</t>
   </si>
   <si>
-    <t xml:space="preserve">Iteration (Sprint) number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acceptance Criteria</t>
+    <t>Iteration (Sprint) number</t>
+  </si>
+  <si>
+    <t>Acceptance Criteria</t>
   </si>
   <si>
     <t>Estimation</t>
@@ -43,19 +53,19 @@
     <t>Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Date started (or planned)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date finished (or planned)</t>
+    <t>Date started (or planned)</t>
+  </si>
+  <si>
+    <t>Date finished (or planned)</t>
   </si>
   <si>
     <t>US-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Create applicant profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a TA applicant
+    <t>Create applicant profile</t>
+  </si>
+  <si>
+    <t>As a TA applicant
 I want to create an applicant profile
 So that I can provide my personal and academic information for recruitment.</t>
   </si>
@@ -66,7 +76,7 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">1. User can register with name, email and student ID
+    <t>1. User can register with name, email and student ID
 2. Profile information is saved to the system
 3. User can edit profile after creation</t>
   </si>
@@ -83,15 +93,15 @@
     <t>US-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Upload CV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a TA applicant
+    <t>Upload CV</t>
+  </si>
+  <si>
+    <t>As a TA applicant
 I want to upload my CV
 So that module organisers can review my qualifications.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. User can upload a PDF CV
+    <t>1. User can upload a PDF CV
 2. File is stored successfully
 3. Uploaded CV can be viewed later</t>
   </si>
@@ -99,15 +109,15 @@
     <t>US-03</t>
   </si>
   <si>
-    <t xml:space="preserve">Browse available jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a TA applicant
+    <t>Browse available jobs</t>
+  </si>
+  <si>
+    <t>As a TA applicant
 I want to browse available TA jobs
 So that I can find suitable opportunities.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Job list is displayed
+    <t>1. Job list is displayed
 2. Each job shows module name and requirements
 3. Users can view job details</t>
   </si>
@@ -118,15 +128,36 @@
     <t>US-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Apply for job</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a TA applicant
+    <t>Search and filter jobs</t>
+  </si>
+  <si>
+    <t>As a TA applicant I want to search and filter available TA jobs So that I can quickly find jobs that match my skills, module preference, or schedule.</t>
+  </si>
+  <si>
+    <t>1. User can enter keywords to search jobs 2. User can filter by module, type of activity, or required skills 3. Filtered/search results are displayed instantly</t>
+  </si>
+  <si>
+    <t>1. On text/CSV/JSON data files only, no database required. 2. Display results instantly; show 'No matching jobs found' if no matches. 3.Supports multi-condition filtering: module, activity type, and skills. 4.Can integrate with AI skill matching later, but not required for this iteration.</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>US-05</t>
+  </si>
+  <si>
+    <t>Apply for job</t>
+  </si>
+  <si>
+    <t>As a TA applicant
 I want to apply for a job
 So that I can be considered for the position.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Applicant can submit application
+    <t>1. Applicant can submit application
 2. Application record is stored
 3. Confirmation message is displayed</t>
   </si>
@@ -134,13 +165,13 @@
     <t>5</t>
   </si>
   <si>
-    <t>US-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check application status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a TA applicant
+    <t>US-06</t>
+  </si>
+  <si>
+    <t>Check application status</t>
+  </si>
+  <si>
+    <t>As a TA applicant
 I want to check my application status
 So that I know whether I am selected.</t>
   </si>
@@ -148,72 +179,66 @@
     <t>Should</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Applicant can see application status
+    <t>1. Applicant can see application status
 2. Status includes pending, accepted, rejected
 3. Status updates when MO makes decision</t>
   </si>
   <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
-    <t>US-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post job</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a module organiser
+    <t>US-07</t>
+  </si>
+  <si>
+    <t>Post job</t>
+  </si>
+  <si>
+    <t>As a module organiser
 I want to post TA job opportunities
 So that students can apply.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. MO can create job listing
+    <t>1. MO can create job listing
 2. Job description and requirements are saved
 3. Job appears in job list</t>
   </si>
   <si>
-    <t>US-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select applicants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a module organiser
+    <t>US-08</t>
+  </si>
+  <si>
+    <t>Select applicants</t>
+  </si>
+  <si>
+    <t>As a module organiser
 I want to select applicants
 So that I can recruit suitable teaching assistants.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. MO can view applicant list
+    <t>1. MO can view applicant list
 2. MO can mark applicant as selected
 3. Selected status updates applicant record</t>
   </si>
   <si>
-    <t>US-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View workload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an administrator
+    <t>US-09</t>
+  </si>
+  <si>
+    <t>View workload</t>
+  </si>
+  <si>
+    <t>As an administrator
 I want to check TA workload
 So that no TA is overloaded.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Admin can view TA assignments
+    <t>1. Admin can view TA assignments
 2. System shows number of assigned jobs
 3. Warning displayed if workload exceeds limit</t>
   </si>
   <si>
-    <t>US-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill matching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a module organiser
+    <t>US-10</t>
+  </si>
+  <si>
+    <t>Skill matching</t>
+  </si>
+  <si>
+    <t>As a module organiser
 I want the system to match applicant skills with job requirements
 So that I can quickly identify suitable candidates.</t>
   </si>
@@ -221,7 +246,7 @@
     <t>Could</t>
   </si>
   <si>
-    <t xml:space="preserve">1. System analyses CV text
+    <t>1. System analyses CV text
 2. Skills are matched with job requirements
 3. Match score is displayed</t>
   </si>
@@ -235,18 +260,18 @@
     <t>2026-04-15</t>
   </si>
   <si>
-    <t>US-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identify missing skills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a TA applicant
+    <t>US-11</t>
+  </si>
+  <si>
+    <t>Identify missing skills</t>
+  </si>
+  <si>
+    <t>As a TA applicant
 I want the system to identify missing skills
 So that I can improve my qualifications.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. System compares CV with job requirements
+    <t>1. System compares CV with job requirements
 2. Missing skills are highlighted
 3. Suggestions are displayed</t>
   </si>
@@ -254,16 +279,167 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1">
-    <font>
-      <sz val="11.000000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -272,24 +448,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor theme="4" tint="0.59999389629810485"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor theme="4" tint="0.599993896298105"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -304,24 +660,312 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="27" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -331,291 +975,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -835,26 +1196,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.7109375"/>
-    <col customWidth="1" min="2" max="2" width="21.8515625"/>
-    <col customWidth="1" min="3" max="3" width="71.421875"/>
-    <col customWidth="1" min="4" max="4" width="7.8515625"/>
-    <col customWidth="1" min="5" max="5" width="3.28125"/>
-    <col customWidth="1" min="6" max="6" width="15.28125"/>
-    <col customWidth="1" min="7" max="7" width="4.28125"/>
-    <col customWidth="1" min="8" max="8" width="2.8515625"/>
-    <col customWidth="1" min="9" max="9" width="11.28125"/>
-    <col customWidth="1" min="10" max="10" width="11.57421875"/>
+    <col min="1" max="1" width="8.70833333333333" customWidth="1"/>
+    <col min="2" max="2" width="21.85" customWidth="1"/>
+    <col min="3" max="3" width="71.425" customWidth="1"/>
+    <col min="4" max="4" width="7.85" customWidth="1"/>
+    <col min="5" max="5" width="3.28333333333333" customWidth="1"/>
+    <col min="6" max="6" width="15.2833333333333" customWidth="1"/>
+    <col min="7" max="7" width="4.28333333333333" customWidth="1"/>
+    <col min="8" max="8" width="2.85" customWidth="1"/>
+    <col min="9" max="9" width="11.2833333333333" customWidth="1"/>
+    <col min="10" max="10" width="11.575" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34.850000000000001" customHeight="1">
+    <row r="1" ht="34.85" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -886,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -915,7 +1274,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -944,7 +1303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -973,7 +1332,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customFormat="1" spans="1:10">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -986,52 +1345,55 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
+      <c r="E5" s="2">
+        <v>2</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
         <v>32</v>
       </c>
       <c r="I5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
         <v>17</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1042,144 +1404,172 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J9" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
       </c>
       <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
         <v>57</v>
       </c>
-      <c r="I10" t="s">
+      <c r="B11" t="s">
         <v>58</v>
       </c>
-      <c r="J10" t="s">
+      <c r="C11" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
+      <c r="D11" t="s">
         <v>60</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" t="s">
-        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
       </c>
       <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" t="s">
         <v>63</v>
       </c>
-      <c r="G11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" t="s">
-        <v>58</v>
-      </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/documents/ProductBacklog_group51.xlsx
+++ b/documents/ProductBacklog_group51.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Recruitment-System-for-TA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8634B86-9DF6-44B9-B075-042690CFBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB96565-DA15-439A-AF91-917CD17D1E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="153">
   <si>
     <t>Story ID</t>
   </si>
@@ -380,10 +380,6 @@
     <t>US-22</t>
   </si>
   <si>
-    <t>Admin dashboard</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1) Only authenticated users can create a profile; 2) Required profile fields validated; 3) Profile saved and retrievable after re-login.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -393,18 +389,6 @@
   </si>
   <si>
     <t>US-23</t>
-  </si>
-  <si>
-    <t>As an administrator
-I want to view recruitment statistics on a dashboard
-So that I can monitor system activity.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Admin can view total applicants
-2. Admin can view number of job postings
-3. Admin can view number of applications submitted</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Manage users</t>
@@ -425,15 +409,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>View system applications</t>
-  </si>
-  <si>
-    <t>As an administrator
-I want to view all job applications
-So that I can monitor recruitment activities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Export recruitment data</t>
   </si>
   <si>
@@ -455,12 +430,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1. Admin can view list of all applications_x000D_
-2. Admin can filter applications by job or applicant_x000D_
-3. Admin can view application status</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1. Admin can export applicant data_x000D_
 2. Admin can export job application records_x000D_
 3. Data can be exported as CSV or Excel file</t>
@@ -613,12 +582,6 @@
   <si>
     <t>AI ranking</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>US-30</t>
-  </si>
-  <si>
-    <t>US-31</t>
   </si>
   <si>
     <t>View system logs</t>
@@ -925,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="8.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.4140625" customWidth="1"/>
@@ -1293,24 +1256,24 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
         <v>47</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G13" t="s">
         <v>16</v>
@@ -1324,22 +1287,22 @@
     </row>
     <row r="14" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
         <v>47</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G14" t="s">
         <v>16</v>
@@ -1353,25 +1316,25 @@
     </row>
     <row r="15" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>113</v>
-      </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G15" t="s">
-        <v>16</v>
+        <v>115</v>
+      </c>
+      <c r="G15" s="3">
+        <v>4</v>
       </c>
       <c r="I15" t="s">
         <v>37</v>
@@ -1382,25 +1345,25 @@
     </row>
     <row r="16" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B16" t="s">
-        <v>114</v>
+        <v>131</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G16" t="s">
-        <v>16</v>
+        <v>146</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3</v>
       </c>
       <c r="I16" t="s">
         <v>37</v>
@@ -1417,7 +1380,7 @@
         <v>116</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
         <v>59</v>
@@ -1426,45 +1389,45 @@
         <v>16</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4</v>
+        <v>125</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="I17" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="J17" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>160</v>
+      <c r="B18" t="s">
+        <v>120</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G18" s="3">
-        <v>3</v>
+        <v>127</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="I18" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="J18" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1475,65 +1438,71 @@
         <v>122</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="G19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="3">
+        <v>3</v>
+      </c>
+      <c r="H19" t="s">
         <v>123</v>
       </c>
       <c r="I19" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="J19" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>132</v>
+        <v>61</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>123</v>
+        <v>13</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="3">
+        <v>3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>64</v>
       </c>
       <c r="I20" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="J20" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>134</v>
+        <v>65</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="D21" t="s">
         <v>13</v>
@@ -1541,14 +1510,14 @@
       <c r="E21" s="3">
         <v>1</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>135</v>
+      <c r="F21" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="G21" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="I21" t="s">
         <v>17</v>
@@ -1562,10 +1531,10 @@
         <v>92</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
@@ -1573,14 +1542,14 @@
       <c r="E22" s="3">
         <v>1</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>63</v>
+      <c r="F22" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="G22" s="3">
         <v>3</v>
       </c>
       <c r="H22" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1594,10 +1563,10 @@
         <v>103</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
@@ -1606,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G23" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1623,77 +1592,77 @@
     </row>
     <row r="24" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>106</v>
+        <v>78</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>105</v>
+        <v>2</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="G24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G25" s="3">
         <v>3</v>
       </c>
       <c r="H25" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
@@ -1702,13 +1671,13 @@
         <v>2</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G26" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s">
         <v>37</v>
@@ -1719,13 +1688,13 @@
     </row>
     <row r="27" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
@@ -1734,13 +1703,13 @@
         <v>2</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G27" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I27" t="s">
         <v>37</v>
@@ -1751,77 +1720,77 @@
     </row>
     <row r="28" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>89</v>
+        <v>136</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E28" s="3">
-        <v>2</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>90</v>
+        <v>3</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="G28" s="3">
-        <v>3</v>
-      </c>
-      <c r="H28" t="s">
-        <v>91</v>
+        <v>5</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="I28" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="J28" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>94</v>
+        <v>139</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E29" s="3">
-        <v>2</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>95</v>
+        <v>3</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="G29" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="I29" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="J29" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" t="s">
         <v>147</v>
       </c>
-      <c r="B30" t="s">
-        <v>142</v>
-      </c>
       <c r="C30" s="5" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D30" t="s">
         <v>59</v>
@@ -1830,84 +1799,28 @@
         <v>3</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G30" s="3">
         <v>5</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="J30" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D31" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="3">
-        <v>3</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G31" s="3">
-        <v>5</v>
-      </c>
-      <c r="H31" t="s">
-        <v>146</v>
-      </c>
-      <c r="I31" t="s">
-        <v>124</v>
-      </c>
-      <c r="J31" t="s">
-        <v>125</v>
-      </c>
+      <c r="C31" s="2"/>
+      <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="B32" t="s">
-        <v>153</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="3">
-        <v>3</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G32" s="3">
-        <v>5</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="I32" t="s">
-        <v>124</v>
-      </c>
-      <c r="J32" t="s">
-        <v>125</v>
-      </c>
+      <c r="C32" s="2"/>
+      <c r="F32" s="2"/>
     </row>
     <row r="33" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="2"/>
@@ -1982,15 +1895,7 @@
       <c r="F50" s="2"/>
     </row>
     <row r="51" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="2"/>
       <c r="F51" s="2"/>
-    </row>
-    <row r="52" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="2"/>
-      <c r="F52" s="2"/>
-    </row>
-    <row r="53" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F53" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/documents/ProductBacklog_group51.xlsx
+++ b/documents/ProductBacklog_group51.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Recruitment-System-for-TA\documents\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB96565-DA15-439A-AF91-917CD17D1E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="157">
   <si>
     <t>Story ID</t>
   </si>
@@ -200,14 +207,17 @@
     <t>Post job</t>
   </si>
   <si>
-    <t>As a module organiser
-I want to post TA job opportunities
-So that students can apply.</t>
-  </si>
-  <si>
-    <t>1. MO can create job listing
-2. Job description and requirements are saved
-3. Job appears in job list</t>
+    <t>As an MO (Module Organiser), I want to post a new TA (Teaching Assistant) vacancy so that students can apply for the position</t>
+  </si>
+  <si>
+    <t>MO can enter module name.
+MO can enter job title (e.g., TA, Tutor).
+MO can provide job description (e.g., responsibilities, tasks).
+MO can define required skills for the position (e.g., communication skills, technical knowledge).
+MO can specify the application deadline.
+MO can choose workload (e.g., weekly hours or tasks).
+MO can click Save to save the vacancy as a draft.
+MO can click Publish to make the vacancy visible to students.</t>
   </si>
   <si>
     <t>US-09</t>
@@ -216,17 +226,31 @@
     <t>Select applicants</t>
   </si>
   <si>
-    <t>As a module organiser
-I want to select applicants
-So that I can recruit suitable teaching assistants.</t>
-  </si>
-  <si>
-    <t>1. MO can view applicant list
-2. MO can mark applicant as selected
-3. Selected status updates applicant record</t>
+    <t>As an MO, I want to select a suitable TA from the applicants so that I can assign them to the position.</t>
+  </si>
+  <si>
+    <t>MO can view the detailed profiles of applicants.
+MO can see skills, experience, and availability for each applicant.
+MO can select one applicant and mark them as selected.
+MO can reject applicants if not selected.
+MO can update the application status to "Selected" or "Rejected".
+MO can notify the selected applicant via email or in the system (if email integration is available).MO can view the detailed profiles of applicants.
+MO can see skills, experience, and availability for each applicant.
+MO can select one applicant and mark them as selected.
+MO can reject applicants if not selected.
+MO can update the application status to "Selected" or "Rejected".
+MO can notify the selected applicant via email or in the system (if email integration is available).</t>
   </si>
   <si>
     <t>US-10</t>
+  </si>
+  <si>
+    <t>View TA workload</t>
+  </si>
+  <si>
+    <t>As an administrator
+I want to check TA workload
+So that no TA is overloaded.</t>
   </si>
   <si>
     <t>1. Admin can view TA assignments
@@ -234,161 +258,23 @@
 3. Warning displayed if workload exceeds limit</t>
   </si>
   <si>
-    <t>Could</t>
-  </si>
-  <si>
-    <t>US-12</t>
-  </si>
-  <si>
-    <t>TA Login</t>
-  </si>
-  <si>
-    <t>As a Teaching Assistant applicant, I want to log in securely so that I can access my profile, CV upload, and job applications.</t>
-  </si>
-  <si>
-    <t>1) Correct credentials authenticate and redirect to applicant area; 2) Incorrect credentials show clear error; 3) Session established for subsequent requests.</t>
-  </si>
-  <si>
-    <t>User management core authentication.</t>
-  </si>
-  <si>
-    <t>TA Logout</t>
-  </si>
-  <si>
-    <t>As a Teaching Assistant applicant, I want to log out so that my account remains secure on shared devices.</t>
-  </si>
-  <si>
-    <t>1) Logout ends session/token; 2) Redirect to login/landing; 3) Back button does not restore authenticated access.</t>
-  </si>
-  <si>
-    <t>Security baseline.</t>
-  </si>
-  <si>
-    <t>US-16</t>
-  </si>
-  <si>
-    <t>Create Applicant Profile</t>
-  </si>
-  <si>
-    <t>Explicit requirement in handout: TA can create an applicant profile.</t>
-  </si>
-  <si>
-    <t>US-17</t>
-  </si>
-  <si>
-    <t>Access Control for Applicant Features</t>
-  </si>
-  <si>
-    <t>As a Teaching Assistant applicant, I want only logged-in users to access profile and application features so that my personal data is protected.</t>
-  </si>
-  <si>
-    <t>1) Unauthenticated access to protected pages redirects to login; 2) After login, return to intended page; 3) Auth checks apply to all protected endpoints.</t>
-  </si>
-  <si>
-    <t>Security requirement for user management.</t>
-  </si>
-  <si>
-    <t>US-18</t>
-  </si>
-  <si>
-    <t>View Applicant Profile</t>
-  </si>
-  <si>
-    <t>As a Teaching Assistant applicant, I want to view my saved profile so that I can confirm what recruiters will see.</t>
-  </si>
-  <si>
-    <t>1) Only authenticated owner can view; 2) Displays latest saved values; 3) Handles missing/incomplete fields gracefully.</t>
-  </si>
-  <si>
-    <t>Supports confidence and transparency.</t>
-  </si>
-  <si>
-    <t>US-19</t>
-  </si>
-  <si>
-    <t>Request Password Reset</t>
-  </si>
-  <si>
-    <t>As a Teaching Assistant applicant, I want to request a password reset so that I can regain access if I forget my password.</t>
-  </si>
-  <si>
-    <t>1) Request via registered email; 2) Response does not reveal whether account exists; 3) Reset token/link generated and expires.</t>
-  </si>
-  <si>
-    <t>Account recovery.</t>
-  </si>
-  <si>
-    <t>US-20</t>
-  </si>
-  <si>
-    <t>Complete Password Reset</t>
-  </si>
-  <si>
-    <t>As a Teaching Assistant applicant, I want to set a new password using a reset link so that I can log in again.</t>
-  </si>
-  <si>
-    <t>1) Valid token allows setting new password; 2) Password meets policy; 3) Token single-use; 4) User can log in with new password.</t>
-  </si>
-  <si>
-    <t>Account recovery completion.</t>
-  </si>
-  <si>
-    <t>US-21</t>
-  </si>
-  <si>
-    <t>Edit Applicant Profile</t>
-  </si>
-  <si>
-    <t>As a Teaching Assistant applicant, I want to edit my profile so that my application details stay accurate.</t>
-  </si>
-  <si>
-    <t>1) Only profile owner can edit; 2) Changes validated and saved; 3) Updated data appears on view page.</t>
-  </si>
-  <si>
-    <t>Completes create/view lifecycle.</t>
+    <t>US-11</t>
   </si>
   <si>
     <t>Balance TA workload</t>
-  </si>
-  <si>
-    <t>View TA workload</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>As an administrator
 I want the system to recommend TAs with lower workload
 So that tasks can be distributed more fairly.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>As an administrator
-I want to check TA workload
-So that no TA is overloaded.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1. System calculates workload of each TA
 2. TAs with lower workload are highlighted
 3. Recommendations appear when assigning jobs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>US-11</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>US-22</t>
-  </si>
-  <si>
-    <t>1) Only authenticated users can create a profile; 2) Required profile fields validated; 3) Profile saved and retrievable after re-login.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>As a Teaching Assistant applicant, I want to create an applicant profile so that I can use the recruitment system to apply for TA opportunities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>US-23</t>
+  </si>
+  <si>
+    <t>US-12</t>
   </si>
   <si>
     <t>Manage users</t>
@@ -397,7 +283,14 @@
     <t>As an administrator
 I want to manage user accounts
 So that I can maintain system security and integrity.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Admin can view list of users
+2. Admin can deactivate or delete user accounts
+3. Admin can view user roles</t>
+  </si>
+  <si>
+    <t>US-13</t>
   </si>
   <si>
     <t>Manage job postings</t>
@@ -406,7 +299,14 @@
     <t>As an administrator
 I want to manage job postings
 So that inappropriate or outdated jobs can be removed.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Admin can view all job postings
+2. Admin can edit job information
+3. Admin can delete job postings</t>
+  </si>
+  <si>
+    <t>US-14</t>
   </si>
   <si>
     <t>Export recruitment data</t>
@@ -415,31 +315,45 @@
     <t>As an administrator
 I want to export recruitment data
 So that I can analyze recruitment results externally.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Admin can view list of users_x000D_
-2. Admin can deactivate or delete user accounts_x000D_
-3. Admin can view user roles</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Admin can view all job postings_x000D_
-2. Admin can edit job information_x000D_
-3. Admin can delete job postings</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Admin can export applicant data_x000D_
-2. Admin can export job application records_x000D_
+  </si>
+  <si>
+    <t>Could</t>
+  </si>
+  <si>
+    <t>1. Admin can export applicant data
+2. Admin can export job application records
 3. Data can be exported as CSV or Excel file</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>US-15</t>
+  </si>
+  <si>
+    <t>View system logs</t>
+  </si>
+  <si>
+    <t>As an administrator
+I want to view system activity logs
+So that I can monitor important actions and ensure system security.</t>
+  </si>
+  <si>
+    <t>1. Admin can view logs of important actions
+2. Logs include user ID, action type, and timestamp
+3. Admin can filter logs by date or user</t>
+  </si>
+  <si>
+    <t>US-16</t>
   </si>
   <si>
     <t>Skill matching</t>
   </si>
   <si>
-    <t>8</t>
+    <t>As an MO, I want the system to suggest potential applicants based on their skills so that I can quickly identify suitable candidates for the position.As an MO, I want the system to suggest potential applicants based on their skills so that I can quickly identify suitable candidates for the position.</t>
+  </si>
+  <si>
+    <t>The system compares job requirements (e.g., skills, experience) with applicant profiles.
+A matching score or label (e.g., High, Medium, Low) is displayed next to each applicant.
+MO can override the system's suggestion and make a final decision manually.
+MO can click on the matching result to view more detailed reasoning behind the match.</t>
   </si>
   <si>
     <t>2026-04-06</t>
@@ -448,63 +362,158 @@
     <t>2026-04-15</t>
   </si>
   <si>
+    <t>US-17</t>
+  </si>
+  <si>
     <t>Identify missing skills</t>
-  </si>
-  <si>
-    <t>US-13</t>
-  </si>
-  <si>
-    <t>TA Registration</t>
-  </si>
-  <si>
-    <t>Supporting story to enable applicant profile creation in TA recruitment system.</t>
-  </si>
-  <si>
-    <t>As a module organiser
-I want the system to match applicant skills with job requirements
-So that I can quickly identify suitable candidates.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. System analyses CV text
-2. Skills are matched with job requirements
-3. Match score is displayed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>As a TA applicant
 I want the system to identify missing skills
 So that I can improve my qualifications.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1. System compares CV with job requirements
 2. Missing skills are highlighted
 3. Suggestions are displayed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>US-18</t>
+  </si>
+  <si>
+    <t>TA Registration</t>
   </si>
   <si>
     <t>As a Teaching Assistant applicant, I want to register an account with basic information so that I can create and access my applicant profile.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.Required fields enforced2.Email format valid &amp; unique 3.Password meets policy 4.On success, account created and user can proceed to login (or is logged in).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>US-14</t>
-  </si>
-  <si>
-    <t>US-15</t>
+  </si>
+  <si>
+    <t>Supporting story to enable applicant profile creation in TA recruitment system.</t>
+  </si>
+  <si>
+    <t>US-19</t>
+  </si>
+  <si>
+    <t>TA Login</t>
+  </si>
+  <si>
+    <t>As a Teaching Assistant applicant, I want to log in securely so that I can access my profile, CV upload, and job applications.</t>
+  </si>
+  <si>
+    <t>1) Correct credentials authenticate and redirect to applicant area; 2) Incorrect credentials show clear error; 3) Session established for subsequent requests.</t>
+  </si>
+  <si>
+    <t>User management core authentication.</t>
+  </si>
+  <si>
+    <t>US-20</t>
+  </si>
+  <si>
+    <t>TA Logout</t>
+  </si>
+  <si>
+    <t>As a Teaching Assistant applicant, I want to log out so that my account remains secure on shared devices.</t>
+  </si>
+  <si>
+    <t>1) Logout ends session/token; 2) Redirect to login/landing; 3) Back button does not restore authenticated access.</t>
+  </si>
+  <si>
+    <t>Security baseline.</t>
+  </si>
+  <si>
+    <t>US-21</t>
+  </si>
+  <si>
+    <t>Create Applicant Profile</t>
+  </si>
+  <si>
+    <t>As a Teaching Assistant applicant, I want to create an applicant profile so that I can use the recruitment system to apply for TA opportunities.</t>
+  </si>
+  <si>
+    <t>1) Only authenticated users can create a profile; 2) Required profile fields validated; 3) Profile saved and retrievable after re-login.</t>
+  </si>
+  <si>
+    <t>Explicit requirement in handout: TA can create an applicant profile.</t>
+  </si>
+  <si>
+    <t>US-22</t>
+  </si>
+  <si>
+    <t>Access Control for Applicant Features</t>
+  </si>
+  <si>
+    <t>As a Teaching Assistant applicant, I want only logged-in users to access profile and application features so that my personal data is protected.</t>
+  </si>
+  <si>
+    <t>1) Unauthenticated access to protected pages redirects to login; 2) After login, return to intended page; 3) Auth checks apply to all protected endpoints.</t>
+  </si>
+  <si>
+    <t>Security requirement for user management.</t>
+  </si>
+  <si>
+    <t>US-23</t>
+  </si>
+  <si>
+    <t>View Applicant Profile</t>
+  </si>
+  <si>
+    <t>As a Teaching Assistant applicant, I want to view my saved profile so that I can confirm what recruiters will see.</t>
+  </si>
+  <si>
+    <t>1) Only authenticated owner can view; 2) Displays latest saved values; 3) Handles missing/incomplete fields gracefully.</t>
+  </si>
+  <si>
+    <t>Supports confidence and transparency.</t>
   </si>
   <si>
     <t>US-24</t>
   </si>
   <si>
+    <t>Request Password Reset</t>
+  </si>
+  <si>
+    <t>As a Teaching Assistant applicant, I want to request a password reset so that I can regain access if I forget my password.</t>
+  </si>
+  <si>
+    <t>1) Request via registered email; 2) Response does not reveal whether account exists; 3) Reset token/link generated and expires.</t>
+  </si>
+  <si>
+    <t>Account recovery.</t>
+  </si>
+  <si>
     <t>US-25</t>
   </si>
   <si>
+    <t>Complete Password Reset</t>
+  </si>
+  <si>
+    <t>As a Teaching Assistant applicant, I want to set a new password using a reset link so that I can log in again.</t>
+  </si>
+  <si>
+    <t>1) Valid token allows setting new password; 2) Password meets policy; 3) Token single-use; 4) User can log in with new password.</t>
+  </si>
+  <si>
+    <t>Account recovery completion.</t>
+  </si>
+  <si>
     <t>US-26</t>
+  </si>
+  <si>
+    <t>Edit Applicant Profile</t>
+  </si>
+  <si>
+    <t>As a Teaching Assistant applicant, I want to edit my profile so that my application details stay accurate.</t>
+  </si>
+  <si>
+    <t>1) Only profile owner can edit; 2) Changes validated and saved; 3) Updated data appears on view page.</t>
+  </si>
+  <si>
+    <t>Completes create/view lifecycle.</t>
   </si>
   <si>
     <t>US-27</t>
@@ -516,7 +525,14 @@
     <t>As a TA applicant
 I want the system to recommend suitable TA jobs
 So that I can quickly find positions that match my skills.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. System analyses applicant profile and CV
+2. System recommends relevant TA jobs
+3. Recommended jobs are displayed on the dashboard</t>
+  </si>
+  <si>
+    <t>AI recommendation feature</t>
   </si>
   <si>
     <t>US-28</t>
@@ -525,40 +541,20 @@
     <t>CV Parsing</t>
   </si>
   <si>
-    <t>AI CV analysis</t>
-  </si>
-  <si>
-    <t>US-29</t>
+    <t>As a TA applicant
+I want the system to extract skills from my uploaded CV
+So that my applicant profile can be automatically populated.</t>
   </si>
   <si>
     <t>1. System analyses uploaded CV text
 2. Skills and education are extracted
 3. Extracted information is stored in applicant profile and can be edited by the user</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>As a TA applicant
-I want the system to extract skills from my uploaded CV
-So that my applicant profile can be automatically populated.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. System analyses applicant profile and CV
-2. System recommends relevant TA jobs
-3. Recommended jobs are displayed on the dashboard</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>As an administrator
-I want to view system activity logs
-So that I can monitor important actions and ensure system security.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Admin can view logs of important actions
-2. Logs include user ID, action type, and timestamp
-3. Admin can filter logs by date or user</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI CV analysis</t>
+  </si>
+  <si>
+    <t>US-29</t>
   </si>
   <si>
     <t>AI applicant ranking</t>
@@ -567,54 +563,207 @@
     <t>As a module organiser
 I want the system to rank applicants automatically
 So that I can quickly identify the most suitable candidates.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1. System analyses CV and job requirements
 2. Applicants receive a ranking score
 3. MO can view ranked applicant list</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI recommendation feature</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>AI ranking</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>View system logs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>US-30</t>
+  </si>
+  <si>
+    <t>View Applicant List</t>
+  </si>
+  <si>
+    <t>As an MO, I want to view a list of applicants who have applied for the TA vacancy so that I can review and compare their qualifications</t>
+  </si>
+  <si>
+    <t>MO can view a list of all applicants for each vacancy.
+Each applicant's name and profile summary (e.g., qualifications, skills) are displayed.
+MO can see application status (e.g., Pending, Shortlisted, Rejected).
+MO can filter applicants by criteria like skills or status.
+MO can click on an applicant's name to view the full profile.MO can view a list of all applicants for each vacancy.
+Each applicant's name and profile summary (e.g., qualifications, skills) are displayed.
+MO can see application status (e.g., Pending, Shortlisted, Rejected).
+MO can filter applicants by criteria like skills or status.
+MO can click on an applicant's name to view the full profile.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -623,12 +772,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -651,9 +980,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
@@ -668,23 +1239,67 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{E9CC1FAC-731F-4A3A-91E7-720D5A87B3FA}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -882,27 +1497,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultColWidth="8.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.08333333333333" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.4140625" customWidth="1"/>
+    <col min="1" max="1" width="8.41666666666667" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="40.1640625" customWidth="1"/>
-    <col min="7" max="7" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="40.1666666666667" customWidth="1"/>
+    <col min="7" max="7" width="18.1666666666667" customWidth="1"/>
     <col min="8" max="8" width="15.75" customWidth="1"/>
     <col min="9" max="9" width="22.75" customWidth="1"/>
-    <col min="10" max="10" width="24.1640625" customWidth="1"/>
+    <col min="10" max="10" width="24.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="48.75" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -934,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="34.15" customHeight="1" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -963,7 +1578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="34.15" customHeight="1" spans="1:10">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -992,7 +1607,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="34.15" customHeight="1" spans="1:10">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1021,7 +1636,7 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="34.15" customHeight="1" spans="1:10">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1050,7 +1665,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" ht="34.15" customHeight="1" spans="1:10">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1082,7 +1697,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" ht="34.15" customHeight="1" spans="1:10">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -1107,11 +1722,11 @@
       <c r="I7" t="s">
         <v>17</v>
       </c>
-      <c r="J7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="4">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="8" ht="34.15" customHeight="1" spans="1:10">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1140,7 +1755,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" ht="34.15" customHeight="1" spans="1:10">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -1162,14 +1777,14 @@
       <c r="G9" t="s">
         <v>43</v>
       </c>
-      <c r="I9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="4">
+        <v>46101</v>
+      </c>
+      <c r="J9" s="4">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="10" ht="34.15" customHeight="1" spans="1:10">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -1182,8 +1797,8 @@
       <c r="D10" t="s">
         <v>13</v>
       </c>
-      <c r="E10" t="s">
-        <v>47</v>
+      <c r="E10">
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>56</v>
@@ -1198,15 +1813,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" ht="33.5" customHeight="1" spans="1:10">
       <c r="A11" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>100</v>
+      <c r="B11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
@@ -1215,7 +1830,7 @@
         <v>47</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
         <v>16</v>
@@ -1227,15 +1842,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>102</v>
+    <row r="12" ht="33.5" customHeight="1" spans="1:10">
+      <c r="A12" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>99</v>
+        <v>62</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
@@ -1243,8 +1858,8 @@
       <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>101</v>
+      <c r="F12" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="G12" t="s">
         <v>43</v>
@@ -1256,15 +1871,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>60</v>
+    <row r="13" ht="33.5" customHeight="1" spans="1:10">
+      <c r="A13" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>108</v>
+        <v>66</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -1272,8 +1887,8 @@
       <c r="E13" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>113</v>
+      <c r="F13" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="G13" t="s">
         <v>16</v>
@@ -1285,15 +1900,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>121</v>
+    <row r="14" ht="33.5" customHeight="1" spans="1:10">
+      <c r="A14" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>110</v>
+        <v>70</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
@@ -1301,8 +1916,8 @@
       <c r="E14" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>114</v>
+      <c r="F14" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="G14" t="s">
         <v>16</v>
@@ -1314,24 +1929,24 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>130</v>
+    <row r="15" ht="33.5" customHeight="1" spans="1:10">
+      <c r="A15" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>112</v>
+        <v>74</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>115</v>
+      <c r="F15" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="G15" s="3">
         <v>4</v>
@@ -1343,24 +1958,24 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>145</v>
+    <row r="16" ht="33.5" customHeight="1" spans="1:10">
+      <c r="A16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>146</v>
+      <c r="F16" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="G16" s="3">
         <v>3</v>
@@ -1372,73 +1987,73 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>69</v>
+    <row r="17" ht="33.5" customHeight="1" spans="1:10">
+      <c r="A17" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>124</v>
+        <v>83</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>117</v>
+      <c r="F17" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="3">
+        <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="J17" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" ht="33.5" customHeight="1" spans="1:10">
+      <c r="A18" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>126</v>
+        <v>89</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>127</v>
+      <c r="F18" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="J18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>77</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" ht="33.5" customHeight="1" spans="1:10">
+      <c r="A19" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>128</v>
+        <v>94</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
@@ -1446,14 +2061,14 @@
       <c r="E19" s="3">
         <v>1</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>129</v>
+      <c r="F19" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="G19" s="3">
         <v>3</v>
       </c>
       <c r="H19" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1462,15 +2077,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>82</v>
+    <row r="20" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A20" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
         <v>13</v>
@@ -1479,13 +2094,13 @@
         <v>1</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="G20" s="3">
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="I20" t="s">
         <v>17</v>
@@ -1494,15 +2109,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>87</v>
+    <row r="21" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A21" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
         <v>13</v>
@@ -1511,13 +2126,13 @@
         <v>1</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="G21" s="3">
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="I21" t="s">
         <v>17</v>
@@ -1526,15 +2141,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>92</v>
+    <row r="22" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A22" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
@@ -1542,14 +2157,14 @@
       <c r="E22" s="3">
         <v>1</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>104</v>
+      <c r="F22" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="G22" s="3">
         <v>3</v>
       </c>
       <c r="H22" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1558,15 +2173,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>103</v>
+    <row r="23" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A23" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
@@ -1575,13 +2190,13 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="G23" s="3">
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1590,15 +2205,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>106</v>
+    <row r="24" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A24" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
         <v>26</v>
@@ -1607,13 +2222,13 @@
         <v>2</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="G24" s="3">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="I24" t="s">
         <v>37</v>
@@ -1622,15 +2237,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>132</v>
+    <row r="25" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A25" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
         <v>26</v>
@@ -1639,13 +2254,13 @@
         <v>2</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G25" s="3">
         <v>3</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="I25" t="s">
         <v>37</v>
@@ -1654,15 +2269,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>133</v>
+    <row r="26" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A26" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
@@ -1671,13 +2286,13 @@
         <v>2</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="G26" s="3">
         <v>3</v>
       </c>
       <c r="H26" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="I26" t="s">
         <v>37</v>
@@ -1686,15 +2301,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+    <row r="27" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A27" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" t="s">
         <v>134</v>
       </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
@@ -1703,13 +2318,13 @@
         <v>2</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="G27" s="3">
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="I27" t="s">
         <v>37</v>
@@ -1718,188 +2333,213 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
-        <v>135</v>
+    <row r="28" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A28" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E28" s="3">
         <v>3</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>144</v>
+      <c r="F28" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="G28" s="3">
         <v>5</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>150</v>
+      <c r="H28" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="I28" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>138</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A29" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E29" s="3">
         <v>3</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>142</v>
+      <c r="F29" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="G29" s="3">
         <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I29" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="J29" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
-        <v>141</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A30" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E30" s="3">
         <v>3</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>149</v>
+      <c r="F30" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="G30" s="3">
         <v>5</v>
       </c>
-      <c r="H30" s="6" t="s">
-        <v>151</v>
+      <c r="H30" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="I30" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="2"/>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" ht="34.15" customHeight="1" spans="1:10">
+      <c r="A31" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="I31" s="4">
+        <v>46101</v>
+      </c>
+      <c r="J31" s="4">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="32" ht="34.15" customHeight="1" spans="1:10">
       <c r="C32" s="2"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" ht="34.15" customHeight="1" spans="3:6">
       <c r="C33" s="2"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" ht="34.15" customHeight="1" spans="3:6">
       <c r="C34" s="2"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" ht="34.15" customHeight="1" spans="3:6">
       <c r="C35" s="2"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" ht="34.15" customHeight="1" spans="3:6">
       <c r="C36" s="2"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" ht="34.15" customHeight="1" spans="3:6">
       <c r="C37" s="2"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" ht="34.15" customHeight="1" spans="3:6">
       <c r="C38" s="2"/>
       <c r="F38" s="2"/>
     </row>
-    <row r="39" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" ht="34.15" customHeight="1" spans="3:6">
       <c r="C39" s="2"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" ht="34.15" customHeight="1" spans="3:6">
       <c r="C40" s="2"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" ht="34.15" customHeight="1" spans="3:6">
       <c r="C41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" ht="34.15" customHeight="1" spans="3:6">
       <c r="C42" s="2"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" ht="34.15" customHeight="1" spans="3:6">
       <c r="C43" s="2"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" ht="34.15" customHeight="1" spans="3:6">
       <c r="C44" s="2"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" ht="34.15" customHeight="1" spans="3:6">
       <c r="C45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" ht="34.15" customHeight="1" spans="3:6">
       <c r="C46" s="2"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" ht="34.15" customHeight="1" spans="3:6">
       <c r="C47" s="2"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" ht="34.15" customHeight="1" spans="3:6">
       <c r="C48" s="2"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" ht="34.15" customHeight="1" spans="3:6">
       <c r="C49" s="2"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" ht="34.15" customHeight="1" spans="3:6">
       <c r="C50" s="2"/>
       <c r="F50" s="2"/>
     </row>
-    <row r="51" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" ht="34.15" customHeight="1" spans="3:6">
       <c r="F51" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/documents/ProductBacklog_group51.xlsx
+++ b/documents/ProductBacklog_group51.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g726\Desktop\叮咚鸡\Recruitment-System-for-TA\documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C2E339-7A6B-4E47-8975-011FAB439974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="163">
   <si>
     <t>Story ID</t>
   </si>
@@ -285,8 +291,8 @@
 So that I can maintain system security and integrity.</t>
   </si>
   <si>
-    <t>1. Admin can view list of users
-2. Admin can deactivate or delete user accounts
+    <t>1. Admin can view list of users_x000D_
+2. Admin can deactivate or delete user accounts_x000D_
 3. Admin can view user roles</t>
   </si>
   <si>
@@ -301,8 +307,8 @@
 So that inappropriate or outdated jobs can be removed.</t>
   </si>
   <si>
-    <t>1. Admin can view all job postings
-2. Admin can edit job information
+    <t>1. Admin can view all job postings_x000D_
+2. Admin can edit job information_x000D_
 3. Admin can delete job postings</t>
   </si>
   <si>
@@ -320,8 +326,8 @@
     <t>Could</t>
   </si>
   <si>
-    <t>1. Admin can export applicant data
-2. Admin can export job application records
+    <t>1. Admin can export applicant data_x000D_
+2. Admin can export job application records_x000D_
 3. Data can be exported as CSV or Excel file</t>
   </si>
   <si>
@@ -541,11 +547,6 @@
     <t>CV Parsing</t>
   </si>
   <si>
-    <t>As a TA applicant
-I want the system to extract skills from my uploaded CV
-So that my applicant profile can be automatically populated.</t>
-  </si>
-  <si>
     <t>1. System analyses uploaded CV text
 2. Skills and education are extracted
 3. Extracted information is stored in applicant profile and can be edited by the user</t>
@@ -560,20 +561,7 @@
     <t>AI applicant ranking</t>
   </si>
   <si>
-    <t>As a module organiser
-I want the system to rank applicants automatically
-So that I can quickly identify the most suitable candidates.</t>
-  </si>
-  <si>
-    <t>1. System analyses CV and job requirements
-2. Applicants receive a ranking score
-3. MO can view ranked applicant list</t>
-  </si>
-  <si>
     <t>AI ranking</t>
-  </si>
-  <si>
-    <t>US-30</t>
   </si>
   <si>
     <t>View Applicant List</t>
@@ -592,18 +580,65 @@
 MO can filter applicants by criteria like skills or status.
 MO can click on an applicant's name to view the full profile.</t>
   </si>
+  <si>
+    <t>US-30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>US-31</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a module organiser
+I want the system to rank applicants automatically
+So that I can quickly identify the most suitable candidates.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a TA applicant
+I want the system to extract skills from my uploaded CV
+So that my applicant profile can be automatically populated.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Applications Manage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a TA applicant
+I want to view a list of positions I have applied for and adjust their priority order
+So that I can inform the MO which positions I prefer to be assigned to first.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Should</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. System analyses CV and job requirements
+2. Applicants receive a ranking score
+3. MO can view ranked applicant list</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. View List: User can view a list of all submitted TA applications
+2. Status Display: Each entry must show the position name and current status
+3. Reorder: User can change the preference order of applications</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Essential for the algorithm to resolve multiple offers</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,155 +650,17 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -772,192 +669,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -980,254 +697,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1238,68 +713,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1497,27 +941,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultColWidth="8.08333333333333" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.41666666666667" customWidth="1"/>
+    <col min="1" max="1" width="8.4375" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="40.1666666666667" customWidth="1"/>
-    <col min="7" max="7" width="18.1666666666667" customWidth="1"/>
+    <col min="6" max="6" width="40.1875" customWidth="1"/>
+    <col min="7" max="7" width="18.1875" customWidth="1"/>
     <col min="8" max="8" width="15.75" customWidth="1"/>
     <col min="9" max="9" width="22.75" customWidth="1"/>
-    <col min="10" max="10" width="24.1666666666667" customWidth="1"/>
+    <col min="10" max="10" width="24.1875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48.75" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1549,86 +993,89 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I3" t="s">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>2</v>
       </c>
+      <c r="H4" s="3"/>
       <c r="I4" s="4">
         <v>46109</v>
       </c>
@@ -1636,28 +1083,29 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="5" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A5" t="s">
+    <row r="5" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>2</v>
       </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="4">
         <v>46101</v>
       </c>
@@ -1665,118 +1113,121 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="6" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A6" t="s">
+    <row r="6" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="7" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="3">
         <v>4</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A7" t="s">
+    <row r="7" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I7" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J7" s="4">
         <v>46108</v>
       </c>
     </row>
-    <row r="8" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A8" t="s">
+    <row r="8" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I8" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A9" t="s">
+    <row r="9" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="H9" s="3"/>
       <c r="I9" s="4">
         <v>46101</v>
       </c>
@@ -1784,762 +1235,800 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="10" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A10" t="s">
+    <row r="10" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="3">
         <v>1</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I10" t="s">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" ht="33.5" customHeight="1" spans="1:10">
-      <c r="A11" t="s">
+    <row r="11" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I11" t="s">
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" ht="33.5" customHeight="1" spans="1:10">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I12" t="s">
+      <c r="H12" s="3"/>
+      <c r="I12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" ht="33.5" customHeight="1" spans="1:10">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I13" t="s">
+      <c r="H13" s="3"/>
+      <c r="I13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" ht="33.5" customHeight="1" spans="1:10">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I14" t="s">
+      <c r="H14" s="3"/>
+      <c r="I14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" ht="33.5" customHeight="1" spans="1:10">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="9" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="3">
         <v>4</v>
       </c>
-      <c r="I15" t="s">
+      <c r="H15" s="3"/>
+      <c r="I15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" ht="33.5" customHeight="1" spans="1:10">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="9" t="s">
         <v>81</v>
       </c>
       <c r="G16" s="3">
         <v>3</v>
       </c>
-      <c r="I16" t="s">
+      <c r="H16" s="3"/>
+      <c r="I16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" ht="33.5" customHeight="1" spans="1:10">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="9" t="s">
         <v>85</v>
       </c>
       <c r="G17" s="3">
         <v>5</v>
       </c>
-      <c r="I17" t="s">
+      <c r="H17" s="3"/>
+      <c r="I17" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="18" ht="33.5" customHeight="1" spans="1:10">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="9" t="s">
         <v>91</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I18" t="s">
+      <c r="H18" s="3"/>
+      <c r="I18" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" ht="33.5" customHeight="1" spans="1:10">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:10" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="3">
         <v>1</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G19" s="3">
         <v>3</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="3">
         <v>1</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="7" t="s">
         <v>101</v>
       </c>
       <c r="G20" s="3">
         <v>3</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="3">
         <v>1</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="7" t="s">
         <v>106</v>
       </c>
       <c r="G21" s="3">
         <v>2</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="3">
         <v>1</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="9" t="s">
         <v>111</v>
       </c>
       <c r="G22" s="3">
         <v>3</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="3">
         <v>1</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="7" t="s">
         <v>116</v>
       </c>
       <c r="G23" s="3">
         <v>3</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="3">
         <v>2</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="7" t="s">
         <v>121</v>
       </c>
       <c r="G24" s="3">
         <v>2</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="3">
         <v>2</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="7" t="s">
         <v>126</v>
       </c>
       <c r="G25" s="3">
         <v>3</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3">
         <v>2</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="7" t="s">
         <v>131</v>
       </c>
       <c r="G26" s="3">
         <v>3</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
         <v>2</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="7" t="s">
         <v>136</v>
       </c>
       <c r="G27" s="3">
         <v>2</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E28" s="3">
         <v>3</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="9" t="s">
         <v>141</v>
       </c>
       <c r="G28" s="3">
         <v>5</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="29" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C29" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E29" s="3">
         <v>3</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>146</v>
+      <c r="F29" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="G29" s="3">
         <v>5</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="I29" t="s">
-        <v>86</v>
-      </c>
-      <c r="J29" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B30" t="s">
-        <v>149</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C30" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E30" s="3">
         <v>3</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>151</v>
+      <c r="F30" s="9" t="s">
+        <v>160</v>
       </c>
       <c r="G30" s="3">
         <v>5</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I30" t="s">
-        <v>86</v>
-      </c>
-      <c r="J30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" ht="34.15" customHeight="1" spans="1:10">
-      <c r="A31" t="s">
-        <v>153</v>
-      </c>
-      <c r="B31" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G31">
+      <c r="G31" s="3">
         <v>5</v>
       </c>
-      <c r="I31" s="4">
+      <c r="H31" s="3"/>
+      <c r="I31" s="5">
         <v>46101</v>
       </c>
       <c r="J31" s="4">
         <v>46108</v>
       </c>
     </row>
-    <row r="32" ht="34.15" customHeight="1" spans="1:10">
-      <c r="C32" s="2"/>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" ht="34.15" customHeight="1" spans="3:6">
+    <row r="32" spans="1:10" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E32" s="3">
+        <v>3</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G32" s="3">
+        <v>3</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="I32" s="4">
+        <v>46118</v>
+      </c>
+      <c r="J32" s="6">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C33" s="2"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" ht="34.15" customHeight="1" spans="3:6">
+    <row r="34" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C34" s="2"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" ht="34.15" customHeight="1" spans="3:6">
+    <row r="35" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C35" s="2"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" ht="34.15" customHeight="1" spans="3:6">
+    <row r="36" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C36" s="2"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" ht="34.15" customHeight="1" spans="3:6">
+    <row r="37" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C37" s="2"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" ht="34.15" customHeight="1" spans="3:6">
+    <row r="38" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C38" s="2"/>
       <c r="F38" s="2"/>
     </row>
-    <row r="39" ht="34.15" customHeight="1" spans="3:6">
+    <row r="39" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C39" s="2"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" ht="34.15" customHeight="1" spans="3:6">
+    <row r="40" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C40" s="2"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" ht="34.15" customHeight="1" spans="3:6">
+    <row r="41" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" ht="34.15" customHeight="1" spans="3:6">
+    <row r="42" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C42" s="2"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" ht="34.15" customHeight="1" spans="3:6">
+    <row r="43" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C43" s="2"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" ht="34.15" customHeight="1" spans="3:6">
+    <row r="44" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C44" s="2"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" ht="34.15" customHeight="1" spans="3:6">
+    <row r="45" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" ht="34.15" customHeight="1" spans="3:6">
+    <row r="46" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C46" s="2"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" ht="34.15" customHeight="1" spans="3:6">
+    <row r="47" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C47" s="2"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" ht="34.15" customHeight="1" spans="3:6">
+    <row r="48" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C48" s="2"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" ht="34.15" customHeight="1" spans="3:6">
+    <row r="49" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C49" s="2"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" ht="34.15" customHeight="1" spans="3:6">
+    <row r="50" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C50" s="2"/>
       <c r="F50" s="2"/>
     </row>
-    <row r="51" ht="34.15" customHeight="1" spans="3:6">
+    <row r="51" spans="3:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F51" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>